--- a/Excel/Datas/passive.xlsx
+++ b/Excel/Datas/passive.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="30240" windowHeight="12920"/>
+    <workbookView windowWidth="23040" windowHeight="10620"/>
   </bookViews>
   <sheets>
     <sheet name="passive_table" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="28">
   <si>
     <t>##var</t>
   </si>
@@ -35,7 +35,10 @@
     <t>id</t>
   </si>
   <si>
-    <t>desc</t>
+    <t>name</t>
+  </si>
+  <si>
+    <t>description</t>
   </si>
   <si>
     <t>##type</t>
@@ -56,7 +59,58 @@
     <t>ID</t>
   </si>
   <si>
-    <t>描述</t>
+    <t>Evolution</t>
+  </si>
+  <si>
+    <t>进化论</t>
+  </si>
+  <si>
+    <t>当己方队伍中的野兽达到2/4/6只时，己方野兽每三次战斗结束后，随机一项属性永久提升1%/3%/5%。</t>
+  </si>
+  <si>
+    <t>Collecting</t>
+  </si>
+  <si>
+    <t>收集癖</t>
+  </si>
+  <si>
+    <t>当己方队伍中的妖怪达到2/4/6只时，己方获取资源时，可以额外获取25%/50%/100%。</t>
+  </si>
+  <si>
+    <t>SpreadSeed</t>
+  </si>
+  <si>
+    <t>散播种子</t>
+  </si>
+  <si>
+    <t>当己方队伍中的植物达到2/4/6只时，己方植物的攻击能对敌方怪兽种植种子（每只敌方怪兽只能被种植至多一颗种子）。在回合结束时，种子能够分别对对应的敌方怪兽造成10/20/30点伤害（此伤害无视防御和适应），并且给所有己方植物分别恢复等量生命。</t>
+  </si>
+  <si>
+    <t>HugeWeapon</t>
+  </si>
+  <si>
+    <t>巨大利器</t>
+  </si>
+  <si>
+    <t>当己方队伍中的昆虫达到1/2/3只时，己方昆虫每攻击4/3/2次，下一次攻击昆虫将造成1.5/2/2.5倍伤害。</t>
+  </si>
+  <si>
+    <t>Loyalty</t>
+  </si>
+  <si>
+    <t>忠诚奉献</t>
+  </si>
+  <si>
+    <t>己方队伍中的机械在生命值低于10%时，会消灭自己并对敌方怪兽造成等同于其最大生命0%的伤害。己方队伍中每额外有一只机械，此伤害增加10%。</t>
+  </si>
+  <si>
+    <t>SuperSpeed</t>
+  </si>
+  <si>
+    <t>超高速</t>
+  </si>
+  <si>
+    <t>当己方队伍中的精灵达到2/4/6只时，己方精灵的攻击能降低敌方怪兽最大防御的5%/10%/20%，并增加所有己方怪兽最大速度的10%/20%/30%。</t>
   </si>
 </sst>
 </file>
@@ -85,8 +139,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
       <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -236,7 +290,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="35">
+  <fills count="36">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -257,6 +311,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -442,7 +502,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="12">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -474,6 +534,21 @@
       </right>
       <top/>
       <bottom style="medium">
+        <color rgb="FFDEE0E3"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFDEE0E3"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFDEE0E3"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFDEE0E3"/>
+      </top>
+      <bottom style="thin">
         <color rgb="FFDEE0E3"/>
       </bottom>
       <diagonal/>
@@ -615,7 +690,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -627,132 +702,123 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -760,6 +826,18 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1088,10 +1166,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:I20"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
   <cols>
     <col min="2" max="2" width="18.5" customWidth="1"/>
-    <col min="3" max="5" width="21.625" customWidth="1"/>
+    <col min="3" max="5" width="21.6296296296296" customWidth="1"/>
     <col min="6" max="9" width="13.5" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1105,12 +1183,14 @@
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1"/>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
       <c r="E1" s="1"/>
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
-      <c r="H1" s="6"/>
-      <c r="I1" s="6"/>
+      <c r="H1" s="2"/>
+      <c r="I1" s="2"/>
     </row>
     <row r="2" spans="1:9">
       <c r="A2" s="1" t="s">
@@ -1127,24 +1207,26 @@
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D3" s="1"/>
+        <v>6</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>6</v>
+      </c>
       <c r="E3" s="1"/>
       <c r="F3" s="1"/>
       <c r="G3" s="1"/>
-      <c r="H3" s="6"/>
-      <c r="I3" s="6"/>
+      <c r="H3" s="2"/>
+      <c r="I3" s="2"/>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
@@ -1155,151 +1237,185 @@
       <c r="H4" s="1"/>
       <c r="I4" s="1"/>
     </row>
-    <row r="5" ht="17.55" spans="1:9">
-      <c r="A5" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B5" s="2" t="s">
+    <row r="5" ht="14.55" spans="1:9">
+      <c r="A5" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="B5" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
-      <c r="F5" s="7"/>
-      <c r="G5" s="7"/>
-      <c r="H5" s="8"/>
-      <c r="I5" s="8"/>
-    </row>
-    <row r="6" spans="2:9">
-      <c r="B6" s="3"/>
-      <c r="C6" s="3"/>
-      <c r="D6" s="4"/>
-      <c r="E6" s="4"/>
+      <c r="C5" s="3"/>
+      <c r="D5" s="3"/>
+      <c r="E5" s="3"/>
+      <c r="F5" s="4"/>
+      <c r="G5" s="4"/>
+      <c r="H5" s="5"/>
+      <c r="I5" s="5"/>
+    </row>
+    <row r="6" ht="13.95" spans="2:9">
+      <c r="B6" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="E6" s="8"/>
       <c r="F6" s="9"/>
       <c r="G6" s="9"/>
       <c r="H6" s="9"/>
       <c r="I6" s="9"/>
     </row>
-    <row r="7" spans="2:9">
-      <c r="B7" s="4"/>
-      <c r="C7" s="4"/>
-      <c r="D7" s="4"/>
-      <c r="E7" s="4"/>
+    <row r="7" ht="13.95" spans="2:9">
+      <c r="B7" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="E7" s="8"/>
       <c r="F7" s="9"/>
       <c r="G7" s="9"/>
       <c r="H7" s="9"/>
       <c r="I7" s="9"/>
     </row>
-    <row r="8" spans="2:9">
-      <c r="B8" s="4"/>
-      <c r="C8" s="4"/>
-      <c r="D8" s="4"/>
-      <c r="E8" s="4"/>
-      <c r="F8" s="5"/>
-      <c r="G8" s="5"/>
-      <c r="H8" s="5"/>
-      <c r="I8" s="5"/>
-    </row>
-    <row r="9" spans="2:9">
-      <c r="B9" s="4"/>
-      <c r="C9" s="4"/>
-      <c r="D9" s="4"/>
-      <c r="E9" s="4"/>
-      <c r="F9" s="5"/>
-      <c r="G9" s="5"/>
-      <c r="H9" s="5"/>
-      <c r="I9" s="5"/>
-    </row>
-    <row r="10" spans="2:9">
-      <c r="B10" s="4"/>
-      <c r="C10" s="4"/>
-      <c r="D10" s="4"/>
-      <c r="E10" s="4"/>
-      <c r="F10" s="5"/>
-      <c r="G10" s="5"/>
-      <c r="H10" s="5"/>
-      <c r="I10" s="5"/>
-    </row>
-    <row r="11" spans="2:9">
-      <c r="B11" s="4"/>
-      <c r="C11" s="4"/>
-      <c r="D11" s="4"/>
-      <c r="E11" s="4"/>
-      <c r="F11" s="5"/>
-      <c r="G11" s="5"/>
-      <c r="H11" s="5"/>
-      <c r="I11" s="5"/>
-    </row>
-    <row r="12" spans="2:9">
-      <c r="B12" s="4"/>
-      <c r="C12" s="4"/>
-      <c r="D12" s="4"/>
-      <c r="E12" s="4"/>
-      <c r="F12" s="5"/>
-      <c r="G12" s="5"/>
-      <c r="H12" s="5"/>
-      <c r="I12" s="5"/>
-    </row>
-    <row r="13" spans="2:9">
-      <c r="B13" s="4"/>
-      <c r="C13" s="4"/>
-      <c r="D13" s="4"/>
-      <c r="E13" s="4"/>
-      <c r="F13" s="5"/>
-      <c r="G13" s="5"/>
-      <c r="H13" s="5"/>
-      <c r="I13" s="5"/>
-    </row>
-    <row r="14" spans="2:9">
-      <c r="B14" s="4"/>
-      <c r="C14" s="4"/>
-      <c r="D14" s="4"/>
-      <c r="E14" s="4"/>
-      <c r="F14" s="5"/>
-      <c r="G14" s="5"/>
-      <c r="H14" s="5"/>
-      <c r="I14" s="5"/>
-    </row>
-    <row r="15" spans="2:9">
-      <c r="B15" s="4"/>
-      <c r="C15" s="4"/>
-      <c r="D15" s="4"/>
-      <c r="E15" s="4"/>
-      <c r="F15" s="5"/>
-      <c r="G15" s="5"/>
-      <c r="H15" s="5"/>
-      <c r="I15" s="5"/>
-    </row>
-    <row r="16" spans="2:9">
-      <c r="B16" s="4"/>
-      <c r="C16" s="4"/>
-      <c r="D16" s="4"/>
-      <c r="E16" s="4"/>
-      <c r="F16" s="5"/>
-      <c r="G16" s="5"/>
-      <c r="H16" s="5"/>
-      <c r="I16" s="5"/>
-    </row>
-    <row r="17" spans="2:9">
-      <c r="B17" s="4"/>
-      <c r="C17" s="4"/>
-      <c r="D17" s="4"/>
-      <c r="E17" s="4"/>
-      <c r="F17" s="5"/>
-      <c r="G17" s="5"/>
-      <c r="H17" s="5"/>
-      <c r="I17" s="5"/>
-    </row>
-    <row r="18" spans="2:2">
-      <c r="B18" s="5"/>
-    </row>
-    <row r="19" spans="2:2">
-      <c r="B19" s="5"/>
-    </row>
-    <row r="20" spans="2:2">
-      <c r="B20" s="5"/>
+    <row r="8" ht="13.95" spans="2:9">
+      <c r="B8" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="E8" s="8"/>
+      <c r="F8" s="10"/>
+      <c r="G8" s="10"/>
+      <c r="H8" s="10"/>
+      <c r="I8" s="10"/>
+    </row>
+    <row r="9" ht="13.95" spans="2:9">
+      <c r="B9" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E9" s="8"/>
+      <c r="F9" s="10"/>
+      <c r="G9" s="10"/>
+      <c r="H9" s="10"/>
+      <c r="I9" s="10"/>
+    </row>
+    <row r="10" ht="13.95" spans="2:9">
+      <c r="B10" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="E10" s="8"/>
+      <c r="F10" s="10"/>
+      <c r="G10" s="10"/>
+      <c r="H10" s="10"/>
+      <c r="I10" s="10"/>
+    </row>
+    <row r="11" ht="13.95" spans="2:9">
+      <c r="B11" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="E11" s="8"/>
+      <c r="F11" s="10"/>
+      <c r="G11" s="10"/>
+      <c r="H11" s="10"/>
+      <c r="I11" s="10"/>
+    </row>
+    <row r="12" ht="14.55" spans="2:9">
+      <c r="B12" s="8"/>
+      <c r="C12" s="8"/>
+      <c r="D12" s="8"/>
+      <c r="E12" s="8"/>
+      <c r="F12" s="10"/>
+      <c r="G12" s="10"/>
+      <c r="H12" s="10"/>
+      <c r="I12" s="10"/>
+    </row>
+    <row r="13" ht="14.55" spans="2:9">
+      <c r="B13" s="8"/>
+      <c r="C13" s="8"/>
+      <c r="D13" s="8"/>
+      <c r="E13" s="8"/>
+      <c r="F13" s="10"/>
+      <c r="G13" s="10"/>
+      <c r="H13" s="10"/>
+      <c r="I13" s="10"/>
+    </row>
+    <row r="14" ht="14.55" spans="2:9">
+      <c r="B14" s="8"/>
+      <c r="C14" s="8"/>
+      <c r="D14" s="8"/>
+      <c r="E14" s="8"/>
+      <c r="F14" s="10"/>
+      <c r="G14" s="10"/>
+      <c r="H14" s="10"/>
+      <c r="I14" s="10"/>
+    </row>
+    <row r="15" ht="14.55" spans="2:9">
+      <c r="B15" s="8"/>
+      <c r="C15" s="8"/>
+      <c r="D15" s="8"/>
+      <c r="E15" s="8"/>
+      <c r="F15" s="10"/>
+      <c r="G15" s="10"/>
+      <c r="H15" s="10"/>
+      <c r="I15" s="10"/>
+    </row>
+    <row r="16" ht="14.55" spans="2:9">
+      <c r="B16" s="8"/>
+      <c r="C16" s="8"/>
+      <c r="D16" s="8"/>
+      <c r="E16" s="8"/>
+      <c r="F16" s="10"/>
+      <c r="G16" s="10"/>
+      <c r="H16" s="10"/>
+      <c r="I16" s="10"/>
+    </row>
+    <row r="17" ht="14.55" spans="2:9">
+      <c r="B17" s="8"/>
+      <c r="C17" s="8"/>
+      <c r="D17" s="8"/>
+      <c r="E17" s="8"/>
+      <c r="F17" s="10"/>
+      <c r="G17" s="10"/>
+      <c r="H17" s="10"/>
+      <c r="I17" s="10"/>
+    </row>
+    <row r="18" ht="14.55" spans="2:2">
+      <c r="B18" s="10"/>
+    </row>
+    <row r="19" ht="14.55" spans="2:2">
+      <c r="B19" s="10"/>
+    </row>
+    <row r="20" ht="14.55" spans="2:2">
+      <c r="B20" s="10"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Excel/Datas/passive.xlsx
+++ b/Excel/Datas/passive.xlsx
@@ -83,7 +83,7 @@
     <t>散播种子</t>
   </si>
   <si>
-    <t>当己方队伍中的植物达到2/4/6只时，己方植物的攻击能对敌方怪兽种植种子（每只敌方怪兽只能被种植至多一颗种子）。在回合结束时，种子能够分别对对应的敌方怪兽造成10/20/30点伤害（此伤害无视防御和适应），并且给所有己方植物分别恢复等量生命。</t>
+    <t>当己方队伍中的植物达到2/4/6只时，己方植物的攻击能对目标敌方怪兽种植种子（每只敌方怪兽只能被种植至多一颗种子）。在回合结束时，种子能够分别对对应的敌方怪兽造成10/20/30点伤害（此伤害无视防御和适应），并且给所有己方植物分别恢复等量生命。</t>
   </si>
   <si>
     <t>HugeWeapon</t>
@@ -110,7 +110,7 @@
     <t>超高速</t>
   </si>
   <si>
-    <t>当己方队伍中的精灵达到2/4/6只时，己方精灵的攻击能降低敌方怪兽最大防御的5%/10%/20%，并增加所有己方怪兽最大速度的10%/20%/30%。</t>
+    <t>己方队伍中的精灵攻击能降低目标敌方怪兽最大速度的10%，并随机增加一只己方怪兽最大速度的10%。</t>
   </si>
 </sst>
 </file>
@@ -814,7 +814,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -836,6 +836,9 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1252,7 +1255,7 @@
       <c r="H5" s="5"/>
       <c r="I5" s="5"/>
     </row>
-    <row r="6" ht="13.95" spans="2:9">
+    <row r="6" ht="14.55" spans="2:9">
       <c r="B6" s="6" t="s">
         <v>10</v>
       </c>
@@ -1268,7 +1271,7 @@
       <c r="H6" s="9"/>
       <c r="I6" s="9"/>
     </row>
-    <row r="7" ht="13.95" spans="2:9">
+    <row r="7" ht="14.55" spans="2:9">
       <c r="B7" s="8" t="s">
         <v>13</v>
       </c>
@@ -1284,23 +1287,23 @@
       <c r="H7" s="9"/>
       <c r="I7" s="9"/>
     </row>
-    <row r="8" ht="13.95" spans="2:9">
+    <row r="8" ht="14.55" spans="2:9">
       <c r="B8" s="8" t="s">
         <v>16</v>
       </c>
       <c r="C8" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="D8" s="7" t="s">
+      <c r="D8" s="10" t="s">
         <v>18</v>
       </c>
       <c r="E8" s="8"/>
-      <c r="F8" s="10"/>
-      <c r="G8" s="10"/>
-      <c r="H8" s="10"/>
-      <c r="I8" s="10"/>
-    </row>
-    <row r="9" ht="13.95" spans="2:9">
+      <c r="F8" s="11"/>
+      <c r="G8" s="11"/>
+      <c r="H8" s="11"/>
+      <c r="I8" s="11"/>
+    </row>
+    <row r="9" ht="14.55" spans="2:9">
       <c r="B9" s="8" t="s">
         <v>19</v>
       </c>
@@ -1311,12 +1314,12 @@
         <v>21</v>
       </c>
       <c r="E9" s="8"/>
-      <c r="F9" s="10"/>
-      <c r="G9" s="10"/>
-      <c r="H9" s="10"/>
-      <c r="I9" s="10"/>
-    </row>
-    <row r="10" ht="13.95" spans="2:9">
+      <c r="F9" s="11"/>
+      <c r="G9" s="11"/>
+      <c r="H9" s="11"/>
+      <c r="I9" s="11"/>
+    </row>
+    <row r="10" ht="14.55" spans="2:9">
       <c r="B10" s="8" t="s">
         <v>22</v>
       </c>
@@ -1327,95 +1330,95 @@
         <v>24</v>
       </c>
       <c r="E10" s="8"/>
-      <c r="F10" s="10"/>
-      <c r="G10" s="10"/>
-      <c r="H10" s="10"/>
-      <c r="I10" s="10"/>
-    </row>
-    <row r="11" ht="13.95" spans="2:9">
+      <c r="F10" s="11"/>
+      <c r="G10" s="11"/>
+      <c r="H10" s="11"/>
+      <c r="I10" s="11"/>
+    </row>
+    <row r="11" ht="14.55" spans="2:9">
       <c r="B11" s="8" t="s">
         <v>25</v>
       </c>
       <c r="C11" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="D11" s="7" t="s">
+      <c r="D11" s="10" t="s">
         <v>27</v>
       </c>
       <c r="E11" s="8"/>
-      <c r="F11" s="10"/>
-      <c r="G11" s="10"/>
-      <c r="H11" s="10"/>
-      <c r="I11" s="10"/>
+      <c r="F11" s="11"/>
+      <c r="G11" s="11"/>
+      <c r="H11" s="11"/>
+      <c r="I11" s="11"/>
     </row>
     <row r="12" ht="14.55" spans="2:9">
       <c r="B12" s="8"/>
       <c r="C12" s="8"/>
       <c r="D12" s="8"/>
       <c r="E12" s="8"/>
-      <c r="F12" s="10"/>
-      <c r="G12" s="10"/>
-      <c r="H12" s="10"/>
-      <c r="I12" s="10"/>
+      <c r="F12" s="11"/>
+      <c r="G12" s="11"/>
+      <c r="H12" s="11"/>
+      <c r="I12" s="11"/>
     </row>
     <row r="13" ht="14.55" spans="2:9">
       <c r="B13" s="8"/>
       <c r="C13" s="8"/>
       <c r="D13" s="8"/>
       <c r="E13" s="8"/>
-      <c r="F13" s="10"/>
-      <c r="G13" s="10"/>
-      <c r="H13" s="10"/>
-      <c r="I13" s="10"/>
+      <c r="F13" s="11"/>
+      <c r="G13" s="11"/>
+      <c r="H13" s="11"/>
+      <c r="I13" s="11"/>
     </row>
     <row r="14" ht="14.55" spans="2:9">
       <c r="B14" s="8"/>
       <c r="C14" s="8"/>
       <c r="D14" s="8"/>
       <c r="E14" s="8"/>
-      <c r="F14" s="10"/>
-      <c r="G14" s="10"/>
-      <c r="H14" s="10"/>
-      <c r="I14" s="10"/>
+      <c r="F14" s="11"/>
+      <c r="G14" s="11"/>
+      <c r="H14" s="11"/>
+      <c r="I14" s="11"/>
     </row>
     <row r="15" ht="14.55" spans="2:9">
       <c r="B15" s="8"/>
       <c r="C15" s="8"/>
       <c r="D15" s="8"/>
       <c r="E15" s="8"/>
-      <c r="F15" s="10"/>
-      <c r="G15" s="10"/>
-      <c r="H15" s="10"/>
-      <c r="I15" s="10"/>
+      <c r="F15" s="11"/>
+      <c r="G15" s="11"/>
+      <c r="H15" s="11"/>
+      <c r="I15" s="11"/>
     </row>
     <row r="16" ht="14.55" spans="2:9">
       <c r="B16" s="8"/>
       <c r="C16" s="8"/>
       <c r="D16" s="8"/>
       <c r="E16" s="8"/>
-      <c r="F16" s="10"/>
-      <c r="G16" s="10"/>
-      <c r="H16" s="10"/>
-      <c r="I16" s="10"/>
+      <c r="F16" s="11"/>
+      <c r="G16" s="11"/>
+      <c r="H16" s="11"/>
+      <c r="I16" s="11"/>
     </row>
     <row r="17" ht="14.55" spans="2:9">
       <c r="B17" s="8"/>
       <c r="C17" s="8"/>
       <c r="D17" s="8"/>
       <c r="E17" s="8"/>
-      <c r="F17" s="10"/>
-      <c r="G17" s="10"/>
-      <c r="H17" s="10"/>
-      <c r="I17" s="10"/>
+      <c r="F17" s="11"/>
+      <c r="G17" s="11"/>
+      <c r="H17" s="11"/>
+      <c r="I17" s="11"/>
     </row>
     <row r="18" ht="14.55" spans="2:2">
-      <c r="B18" s="10"/>
+      <c r="B18" s="11"/>
     </row>
     <row r="19" ht="14.55" spans="2:2">
-      <c r="B19" s="10"/>
+      <c r="B19" s="11"/>
     </row>
     <row r="20" ht="14.55" spans="2:2">
-      <c r="B20" s="10"/>
+      <c r="B20" s="11"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
